--- a/nriss-patch-2/ig/StructureDefinition-fr-medication-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-medication-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:58:47+00:00</t>
+    <t>2026-08-04T07:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/StructureDefinition-fr-medication-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-medication-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="332">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:44:41+00:00</t>
+    <t>2026-08-07T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -503,6 +503,39 @@
     <t>Any characteristic of the medicinal product prescribed or dispensed (for example, price, textual package description, special program information, etc)</t>
   </si>
   <si>
+    <t>Medication.extension:unitOfPresentation</t>
+  </si>
+  <si>
+    <t>unitOfPresentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-unitofpresentation|1.0.0-comment-2}
+</t>
+  </si>
+  <si>
+    <t>Unité de présentation du produit de santé (comprimé, ampoule, tube). En général, le plus petit objet dénombrable du package.
+EDQM Standard Terms (0.4.0.127.0.16.1.1.2.1) / classe UOP (Unit of Presentation)..</t>
+  </si>
+  <si>
+    <t>Unit of presentation, typically describing the smallest countable package item (e.g tablet, vial, ampoule, etc). Unit of presentation is also often used in describing pack size and the denominator of strength. If the size of presentation unit is relevant, it should be described in sizeOfItem extension.</t>
+  </si>
+  <si>
+    <t>Medication.extension:sizeOfItem</t>
+  </si>
+  <si>
+    <t>sizeOfItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-sizeofitem|1.0.0-comment-2}
+</t>
+  </si>
+  <si>
+    <t>Quantité de produit par unité (ex : 3 ml / 1 flacon).</t>
+  </si>
+  <si>
+    <t>Size of a manufactured item or unit of presentation. For example, size of one vial in a package that may contain several vials.</t>
+  </si>
+  <si>
     <t>Medication.modifierExtension</t>
   </si>
   <si>
@@ -928,6 +961,22 @@
   </si>
   <si>
     <t>Medication.ingredient.strength.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.extension:basisOfStrengthSubstance</t>
+  </si>
+  <si>
+    <t>basisOfStrengthSubstance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-strengthsubstance|1.0.0-comment-2}
+</t>
+  </si>
+  <si>
+    <t>Substance concernée.</t>
+  </si>
+  <si>
+    <t>Substance for marking the basis of strength. When the precise active ingredient is a salt, the strength is often provided for the active moiety (basis of strength).</t>
   </si>
   <si>
     <t>Medication.ingredient.strength.numerator</t>
@@ -1330,12 +1379,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.4140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.77734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="21.7734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1343,7 +1392,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="98.9921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2742,48 +2791,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
       </c>
@@ -2831,7 +2878,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2849,7 +2896,7 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2858,14 +2905,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
       </c>
@@ -2874,29 +2923,27 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2945,7 +2992,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2957,61 +3004,63 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I15" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3035,13 +3084,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>77</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3059,39 +3108,39 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3102,7 +3151,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3111,18 +3160,20 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3171,71 +3222,71 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3261,63 +3312,63 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3328,7 +3379,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3337,23 +3388,19 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>196</v>
-      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3377,11 +3424,13 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3399,50 +3448,50 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -3451,23 +3500,21 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3503,51 +3550,51 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3558,30 +3605,32 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3605,13 +3654,11 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -3629,13 +3676,13 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
@@ -3647,21 +3694,21 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3684,16 +3731,20 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -3756,24 +3807,24 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3787,25 +3838,25 @@
         <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I22" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J22" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3831,11 +3882,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -3853,7 +3906,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3868,24 +3921,24 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3908,13 +3961,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3965,7 +4018,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3980,24 +4033,24 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4008,10 +4061,10 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
@@ -4020,16 +4073,16 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4055,13 +4108,11 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4079,13 +4130,13 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
@@ -4094,24 +4145,24 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4131,16 +4182,16 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>181</v>
+        <v>244</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>182</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>183</v>
+        <v>246</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4191,7 +4242,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4203,13 +4254,13 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4220,14 +4271,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4246,16 +4297,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>132</v>
+        <v>249</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>187</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>158</v>
+        <v>252</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4305,7 +4356,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>190</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4317,13 +4368,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4334,46 +4385,42 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4421,25 +4468,25 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>194</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4450,21 +4497,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4476,18 +4523,18 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>252</v>
+        <v>132</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4523,84 +4570,86 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AC28" s="2"/>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
+      <c r="B29" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I29" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O29" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4625,11 +4674,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4647,39 +4698,39 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>258</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4687,7 +4738,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
@@ -4702,16 +4753,18 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>181</v>
+        <v>262</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>182</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -4747,22 +4800,20 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>87</v>
@@ -4771,41 +4822,43 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
@@ -4814,18 +4867,18 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>187</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -4849,63 +4902,61 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4916,7 +4967,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -4925,23 +4976,19 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>196</v>
-      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -4989,75 +5036,73 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>197</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5093,55 +5138,53 @@
         <v>77</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5150,29 +5193,31 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K34" t="s" s="2">
-        <v>275</v>
+        <v>202</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>253</v>
+        <v>203</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5221,13 +5266,13 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
@@ -5236,24 +5281,24 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>259</v>
+        <v>211</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5267,26 +5312,28 @@
         <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>277</v>
+        <v>191</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5335,7 +5382,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5353,23 +5400,25 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>281</v>
+        <v>218</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5390,16 +5439,18 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>234</v>
+        <v>285</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5447,10 +5498,10 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>87</v>
@@ -5462,24 +5513,24 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>285</v>
+        <v>186</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5502,16 +5553,18 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>183</v>
+        <v>289</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5559,7 +5612,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>184</v>
+        <v>286</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5571,13 +5624,13 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5586,26 +5639,26 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>77</v>
@@ -5614,17 +5667,15 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5661,51 +5712,51 @@
         <v>77</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>190</v>
+        <v>292</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>77</v>
+        <v>296</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5713,28 +5764,28 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>290</v>
+        <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>291</v>
+        <v>192</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5785,7 +5836,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>293</v>
+        <v>194</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5797,13 +5848,13 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>294</v>
+        <v>195</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5812,43 +5863,45 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>290</v>
+        <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>296</v>
+        <v>197</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -5885,53 +5938,55 @@
         <v>77</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" hidden="true">
-      <c r="A41" t="s" s="2">
+      <c r="C41" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="B41" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>77</v>
       </c>
@@ -5943,7 +5998,7 @@
         <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>77</v>
@@ -5952,13 +6007,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6009,25 +6064,25 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6036,7 +6091,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>304</v>
       </c>
@@ -6049,28 +6104,28 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>181</v>
+        <v>305</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>182</v>
+        <v>306</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>183</v>
+        <v>307</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6121,7 +6176,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>184</v>
+        <v>308</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6133,13 +6188,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>185</v>
+        <v>309</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6148,45 +6203,43 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>132</v>
+        <v>305</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>187</v>
+        <v>311</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6235,25 +6288,25 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>190</v>
+        <v>313</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6264,46 +6317,42 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>132</v>
+        <v>249</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>248</v>
+        <v>316</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6351,25 +6400,25 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>130</v>
+        <v>318</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6378,12 +6427,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6397,7 +6446,7 @@
         <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
@@ -6406,13 +6455,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>308</v>
+        <v>192</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>309</v>
+        <v>193</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6463,7 +6512,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>307</v>
+        <v>194</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6475,41 +6524,41 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>310</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>77</v>
@@ -6518,15 +6567,17 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>312</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>313</v>
+        <v>197</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6575,35 +6626,375 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>311</v>
+        <v>200</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AI46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
+      <c r="H48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK46" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>316</v>
+      <c r="AK48" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN46">
+  <autoFilter ref="A1:AN49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6613,7 +7004,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI45">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
